--- a/系统进化清单.xlsx
+++ b/系统进化清单.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\claude\workstation\interview-coach - 副本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\claude\workstation\interview-coach\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
   <si>
     <t>改进内容</t>
   </si>
@@ -49,6 +49,42 @@
   </si>
   <si>
     <t>实现时间</t>
+  </si>
+  <si>
+    <t>岗位分析时，岗位描述太长，会出现超时情况</t>
+  </si>
+  <si>
+    <t>2026.8.4</t>
+  </si>
+  <si>
+    <t>面试结束环节，有问题但是不能回答，鉴于模拟面试实际上提问的问题意义不大，直接改成面试结束提示，并提醒有可能在真实面试中可能会存在答疑环节。</t>
+  </si>
+  <si>
+    <t>岗位分析页面创建分析成功后，页面没有退出，会导致误解，用户认为没有添加成功而造成重复添加。</t>
+  </si>
+  <si>
+    <t>AI生成的问题使用太多专业性术语，增加面试者负担，问题过长，建议一次只问一个问题，多生成几个问题。</t>
+  </si>
+  <si>
+    <t>多次面试层次发展，将前几次评估结果作为参考标准放在提示词中，避免每次面试都会问同样的问题，没有起到加强技能的效果。</t>
+  </si>
+  <si>
+    <t>岗位同质化去重，避免相近岗位占用过多空间</t>
+  </si>
+  <si>
+    <t>简历与岗位的匹配通过RAG来提升匹配度</t>
+  </si>
+  <si>
+    <t>增加多态输入</t>
+  </si>
+  <si>
+    <t>minio应用：
+    1.简历存储
+ 2.报告存储（不直接存在数据库中了，而是从Minio中读取出来展示）</t>
+  </si>
+  <si>
+    <t>控制llm并发：
+ 1.用数据库+redis控制岗位分析/简历分析，采用按用户轮询。</t>
   </si>
 </sst>
 </file>
@@ -700,22 +736,22 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1028,10 +1064,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="35" style="1" customWidth="1"/>
+    <col min="1" max="1" width="67" style="1" customWidth="1"/>
     <col min="2" max="2" width="29.0909090909091" style="2" customWidth="1"/>
     <col min="3" max="3" width="33.9090909090909" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.4545454545455" style="3" customWidth="1"/>
@@ -1053,6 +1089,86 @@
       </c>
       <c r="E1" s="5" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" ht="42" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" ht="28" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" ht="28" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" ht="28" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" ht="42" spans="1:5">
+      <c r="A10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" ht="28" spans="1:5">
+      <c r="A11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/系统进化清单.xlsx
+++ b/系统进化清单.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="19">
   <si>
     <t>改进内容</t>
   </si>
@@ -85,6 +85,15 @@
   <si>
     <t>控制llm并发：
  1.用数据库+redis控制岗位分析/简历分析，采用按用户轮询。</t>
+  </si>
+  <si>
+    <t>同时在用人数过多，导致LLM爆炸</t>
+  </si>
+  <si>
+    <t>2026.8.5</t>
+  </si>
+  <si>
+    <t>增加当前在线面试人数显示，并对当前在线面试人数进行控制，以防LLM用量爆炸</t>
   </si>
 </sst>
 </file>
@@ -1064,7 +1073,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="67" style="1" customWidth="1"/>
@@ -1169,6 +1178,17 @@
       </c>
       <c r="B11" s="2" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="12" ht="42" spans="1:5">
+      <c r="A12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/系统进化清单.xlsx
+++ b/系统进化清单.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
   <si>
     <t>改进内容</t>
   </si>
@@ -93,7 +93,17 @@
     <t>2026.8.5</t>
   </si>
   <si>
-    <t>增加当前在线面试人数显示，并对当前在线面试人数进行控制，以防LLM用量爆炸</t>
+    <t>- 主控：Redis 分布式计数信号量
+- 限制同时在线面试人数
+- 满了进入等待队列或返回繁忙提示
+- 辅控：LLM API 令牌桶/滑动窗口
+- 保护 LLM provider 的 RPM/TPM/并发上限
+- 放在 LlmInterviewService 调用入口
+- 兜底：Redis TTL + finally 释放
+- 防止 SSE 异常断开导致槽位死锁</t>
+  </si>
+  <si>
+    <t>是</t>
   </si>
 </sst>
 </file>
@@ -760,6 +770,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1180,15 +1193,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" ht="42" spans="1:5">
+    <row r="12" ht="182" spans="1:5">
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="7" t="s">
         <v>18</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
